--- a/test/list/rajadesa/tanjungsari/list_tanjungsari_2.xlsx
+++ b/test/list/rajadesa/tanjungsari/list_tanjungsari_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\dds req\list\rajadesa\tanjungsari\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\rajadesa\tanjungsari\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB70EC3F-1E15-424C-86AE-5E78107B141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6087E8-96C8-462B-B7D2-7FFD529D0F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="180">
   <si>
     <t>nama</t>
   </si>
@@ -124,490 +124,448 @@
     <t>Sindangjaya</t>
   </si>
   <si>
-    <t>Jalan di sekitar lingkungan kami berlubang dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Sampah di taman umum tidak dibersihkan secara teratur.</t>
-  </si>
-  <si>
-    <t>Sistem drainase di daerah kami tidak berfungsi dengan baik saat hujan.</t>
-  </si>
-  <si>
-    <t>Ada kebisingan berlebihan dari pabrik yang mengganggu kenyamanan tinggal kami.</t>
-  </si>
-  <si>
-    <t>Fasilitas olahraga seperti lapangan sepak bola dan lapangan basket rusak dan tidak diperbaiki.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat penampungan sampah yang cukup di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Air minum dari kran di rumah kami terasa kotor dan berbau.</t>
-  </si>
-  <si>
-    <t>Sekolah setempat kurang memadai dalam menyediakan fasilitas pendidikan yang memadai.</t>
-  </si>
-  <si>
-    <t>Gang-gang di lingkungan kami tidak terawat dan menjadi sarang nyamuk.</t>
-  </si>
-  <si>
-    <t>Perluasan jalan di sekitar kami menyebabkan kemacetan lalu lintas yang parah.</t>
-  </si>
-  <si>
-    <t>Kualitas udara di lingkungan kami buruk karena polusi kendaraan.</t>
-  </si>
-  <si>
-    <t>Listrik sering mati dan pemadaman berlangsung lama di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada fasilitas kesehatan yang memadai di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Tingkat kejahatan di lingkungan kami meningkat dan perlu keamanan yang lebih baik.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat bermain untuk anak-anak di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Kualitas air di sungai atau danau terdekat tercemar dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Ruang publik seperti taman dan area hijau tidak dirawat dengan baik.</t>
-  </si>
-  <si>
-    <t>Kualitas penerangan di jalan-jalan kami buruk dan perlu ditingkatkan.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat parkir yang memadai di sekitar toko dan pusat perbelanjaan.</t>
-  </si>
-  <si>
-    <t>Internet di daerah kami tidak stabil dan sering putus.</t>
-  </si>
-  <si>
-    <t>Tidak adanya aksesibilitas bagi orang dengan kebutuhan khusus di tempat umum.</t>
-  </si>
-  <si>
-    <t>Binatang liar seperti anjing liar menjadi masalah di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada jalur pejalan kaki yang aman di sekitar jalan-jalan utama.</t>
-  </si>
-  <si>
-    <t>Tidak adanya ruang terbuka hijau yang cukup di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Bangunan yang ditinggalkan dan tidak terawat di sekitar kami menjadi tempat tinggal bagi tikus dan serangga.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat ibadah yang memadai di daerah kami.</t>
-  </si>
-  <si>
-    <t>Lampu jalan di depan rumah saya tidak menyala ketika malam.</t>
-  </si>
-  <si>
-    <t>Rute angkutan umum ke daerah kami tidak memadai untuk masyarakat.</t>
-  </si>
-  <si>
-    <t>Kurangnya lapangan kerja di lingkungan kami membuat ekonomi warga sulit.</t>
-  </si>
-  <si>
-    <t>Tidak ada layanan angkutan umum pada larut malam di wilayah kami.</t>
-  </si>
-  <si>
-    <t>NURHAYATI</t>
-  </si>
-  <si>
-    <t>AAS HERMAWAN</t>
-  </si>
-  <si>
-    <t>THOLIB</t>
-  </si>
-  <si>
-    <t>ENJUM</t>
-  </si>
-  <si>
-    <t>H. IHWAN</t>
-  </si>
-  <si>
-    <t>DARMAD</t>
-  </si>
-  <si>
-    <t>UUN UNAESIH</t>
-  </si>
-  <si>
-    <t>ALVI SYAHRI</t>
-  </si>
-  <si>
-    <t>GERI ABSORI</t>
-  </si>
-  <si>
-    <t>KARSIJA</t>
-  </si>
-  <si>
-    <t>ENE</t>
-  </si>
-  <si>
-    <t>SITI WAKIAH</t>
-  </si>
-  <si>
-    <t>ROHIM</t>
-  </si>
-  <si>
-    <t>YUYUM</t>
-  </si>
-  <si>
-    <t>LENA APRILIANA</t>
-  </si>
-  <si>
-    <t>AAY HERLIANA</t>
-  </si>
-  <si>
-    <t>LENI APRILIANI</t>
-  </si>
-  <si>
-    <t>IRUN</t>
-  </si>
-  <si>
-    <t>ELIN SITI NURLINA</t>
-  </si>
-  <si>
-    <t>AHMAD RIFAI SYAMBAS</t>
-  </si>
-  <si>
-    <t>MUZDALIFAH</t>
-  </si>
-  <si>
     <t>ANWAR</t>
   </si>
   <si>
-    <t>HARUN</t>
-  </si>
-  <si>
-    <t>SARI`AH</t>
-  </si>
-  <si>
-    <t>NAZWATUR RAFIDAH</t>
-  </si>
-  <si>
-    <t>FITRIYANA HAYATILAH</t>
-  </si>
-  <si>
-    <t>MUZAKI</t>
-  </si>
-  <si>
-    <t>INAH</t>
-  </si>
-  <si>
-    <t>SURDI</t>
-  </si>
-  <si>
-    <t>OMOH</t>
-  </si>
-  <si>
-    <t>ABDULAH</t>
-  </si>
-  <si>
-    <t>NIA KURNIASIH</t>
-  </si>
-  <si>
-    <t>NOVA ARDIANSAH</t>
-  </si>
-  <si>
-    <t>SOPI NURHIDAYAHM</t>
-  </si>
-  <si>
-    <t>MISNAH</t>
-  </si>
-  <si>
-    <t>SUTAR</t>
-  </si>
-  <si>
-    <t>RUKINI</t>
-  </si>
-  <si>
-    <t>EVI ASRI ROSTIKA</t>
-  </si>
-  <si>
-    <t>UJU JUNAEDI</t>
-  </si>
-  <si>
-    <t>NUNUNG</t>
-  </si>
-  <si>
-    <t>ADE INAYAH</t>
-  </si>
-  <si>
-    <t>NURUL ANISA</t>
-  </si>
-  <si>
-    <t>EMAN</t>
-  </si>
-  <si>
-    <t>HASAN</t>
-  </si>
-  <si>
-    <t>MAEMUNAH</t>
-  </si>
-  <si>
-    <t>ROHIMIN</t>
-  </si>
-  <si>
-    <t>ADE AMRI MUBAROK</t>
-  </si>
-  <si>
-    <t>IMAS MASITOH</t>
-  </si>
-  <si>
-    <t>ARDIAN MAULANA</t>
-  </si>
-  <si>
-    <t>SOLIHIN</t>
-  </si>
-  <si>
-    <t>MAKIAH</t>
-  </si>
-  <si>
-    <t>SISKA PEBRIYANI</t>
-  </si>
-  <si>
-    <t>SUSILAWATI</t>
-  </si>
-  <si>
-    <t>ABDUL</t>
-  </si>
-  <si>
-    <t>KESAH</t>
-  </si>
-  <si>
-    <t>AGUS ISMAIL</t>
-  </si>
-  <si>
-    <t>RAMAD</t>
-  </si>
-  <si>
-    <t>SARTIMI</t>
-  </si>
-  <si>
-    <t>KARNA</t>
-  </si>
-  <si>
-    <t>MIS`AH</t>
-  </si>
-  <si>
-    <t>IDI</t>
-  </si>
-  <si>
-    <t>ISOH</t>
-  </si>
-  <si>
-    <t>ALDIANSYAH</t>
-  </si>
-  <si>
-    <t>DODO</t>
-  </si>
-  <si>
     <t>YATI</t>
   </si>
   <si>
-    <t>LUTFI AENIAH</t>
-  </si>
-  <si>
-    <t>REZA AFIFAN</t>
-  </si>
-  <si>
-    <t>EDI SUHENDI</t>
-  </si>
-  <si>
-    <t>N. PATONAH</t>
-  </si>
-  <si>
-    <t>DIDA YUNIAR</t>
-  </si>
-  <si>
-    <t>REIHAN ENDI SUANDI</t>
-  </si>
-  <si>
-    <t>MUHAMAD SUDARSONO</t>
-  </si>
-  <si>
-    <t>SITI AISAH</t>
-  </si>
-  <si>
-    <t>ALIF GUMILANG</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas belajar yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Buku teks dan materi pembelajaran yang digunakan sudah usang dan tidak diperbarui.</t>
-  </si>
-  <si>
-    <t>Tingkat kualitas pengajaran guru di beberapa sekolah rendah.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan keterampilan hidup yang diajarkan di sekolah.</t>
-  </si>
-  <si>
-    <t>Overcrowding (kepadatan) di kelas-kelas sehingga siswa tidak mendapatkan perhatian yang cukup dari guru.</t>
-  </si>
-  <si>
-    <t>Kurangnya aksesibilitas untuk siswa dengan kebutuhan khusus di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Program kurikulum yang tidak relevan dengan kebutuhan dunia kerja.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan sumber daya untuk siswa yang berprestasi akademik.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk terlibat dalam kegiatan ekstrakurikuler.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan dan pembinaan untuk guru baru yang masuk.</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas laboratorium ilmiah dan komputer di sekolah kami.</t>
-  </si>
-  <si>
-    <t>Kualitas makanan di kantin sekolah kami tidak sehat dan tidak bergizi.</t>
-  </si>
-  <si>
-    <t>Banyak siswa yang melakukan pelecehan atau kekerasan di lingkungan sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan pemahaman bagi siswa dengan masalah kesehatan mental.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pengembangan keterampilan kepemimpinan dan kolaborasi di sekolah.</t>
-  </si>
-  <si>
-    <t>Banyaknya kegiatan pengajaran yang terlalu terfokus pada tes dan bukan pada pemahaman konsep.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian terhadap seni dan musik di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program bantuan atau beasiswa bagi siswa yang kurang mampu secara finansial.</t>
-  </si>
-  <si>
-    <t>Kurangnya guru yang berkualitas dan terlatih di beberapa sekolah pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana transportasi bagi siswa yang tinggal di daerah terpencil.</t>
-  </si>
-  <si>
-    <t>Tingkat disiplin yang rendah di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya pendekatan individual dalam pembelajaran bagi siswa dengan kecepatan belajar yang berbeda.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk berpartisipasi dalam pertukaran pelajar atau program internasional.</t>
-  </si>
-  <si>
-    <t>Kurangnya keterlibatan orang tua dalam pendidikan anak-anak mereka.</t>
-  </si>
-  <si>
-    <t>Tidak adanya konseling karir yang memadai untuk siswa-siswa kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya penekanan pada pendidikan karakter dan etika di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Sistem penilaian yang tidak adil dan kurang transparan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembaruan teknologi pendidikan di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Banyaknya siswa yang putus sekolah atau tidak melanjutkan pendidikan ke jenjang yang lebih tinggi.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program vokasional yang memadai untuk siswa yang tidak melanjutkan ke perguruan tinggi.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana perpustakaan yang memadai di beberapa sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian pada pendidikan inklusif untuk siswa dengan kebutuhan khusus.</t>
-  </si>
-  <si>
-    <t>Kurangnya pemahaman tentang pentingnya pendidikan seksual yang komprehensif.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan penggunaan teknologi bagi guru dan siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan tentang keberlanjutan dan lingkungan hidup.</t>
-  </si>
-  <si>
-    <t>Ketidakadilan dalam alokasi dana pendidikan antara daerah perkotaan dan pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya transparansi dalam penggunaan dana pendidikan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembinaan keterampilan kewirausahaan bagi siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan untuk pendidikan seni dan budaya.</t>
-  </si>
-  <si>
-    <t>Tidak adanya akses internet yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya penanganan kasus bullying dan kekerasan di sekolah secara tegas.</t>
-  </si>
-  <si>
-    <t>Kurangnya kerjasama antara sekolah dan komunitas lokal.</t>
-  </si>
-  <si>
-    <t>Kurangnya program mentorship atau bimbingan akademik bagi siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya peluang untuk pengembangan kepemimpinan siswa dalam kegiatan sekolah.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program pendidikan tentang keuangan pribadi dan pengelolaan uang.</t>
-  </si>
-  <si>
-    <t>2023-07-11</t>
-  </si>
-  <si>
-    <t>2023-07-12</t>
-  </si>
-  <si>
-    <t>2023-07-13</t>
-  </si>
-  <si>
-    <t>2023-07-14</t>
-  </si>
-  <si>
-    <t>2023-07-15</t>
-  </si>
-  <si>
-    <t>2023-07-17</t>
-  </si>
-  <si>
-    <t>2023-07-18</t>
-  </si>
-  <si>
-    <t>2023-07-19</t>
-  </si>
-  <si>
-    <t>2023-07-20</t>
-  </si>
-  <si>
-    <t>2023-07-21</t>
-  </si>
-  <si>
-    <t>2023-07-22</t>
-  </si>
-  <si>
-    <t>2023-07-24</t>
-  </si>
-  <si>
-    <t>2023-07-25</t>
+    <t>Harga kebutuhan pokok terus meroket, sulit untuk mencukupi.</t>
+  </si>
+  <si>
+    <t>Pengangguran tinggi, sulit mencari pekerjaan yang layak.</t>
+  </si>
+  <si>
+    <t>Upah minimum belum cukup untuk memenuhi kebutuhan hidup.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses kepada layanan kesehatan karena biaya yang tinggi.</t>
+  </si>
+  <si>
+    <t>Pendidikan berkualitas sulit dijangkau akibat biaya tinggi.</t>
+  </si>
+  <si>
+    <t>Besarnya beban pajak dan kurangnya manfaat yang dirasakan.</t>
+  </si>
+  <si>
+    <t>Harga sewa tempat tinggal terlalu tinggi di perkotaan.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan kredit untuk usaha kecil dan menengah.</t>
+  </si>
+  <si>
+    <t>Inflasi yang tidak terkendali menggerus daya beli.</t>
+  </si>
+  <si>
+    <t>Kesenjangan ekonomi antara kaya dan miskin semakin melebar.</t>
+  </si>
+  <si>
+    <t>Harga BBM dan energi terus naik, mengganggu mobilitas.</t>
+  </si>
+  <si>
+    <t>Keterbatasan peluang ekonomi di daerah pedesaan menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses modal untuk pertanian modern di desa.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja di sektor industri kreatif.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya transportasi umum merugikan pekerja.</t>
+  </si>
+  <si>
+    <t>Sulitnya memenuhi kebutuhan pensiun di tengah kenaikan biaya hidup.</t>
+  </si>
+  <si>
+    <t>Rendahnya kualitas infrastruktur di beberapa daerah.</t>
+  </si>
+  <si>
+    <t>Hambatan birokrasi dan korupsi menghambat perkembangan usaha.</t>
+  </si>
+  <si>
+    <t>Investasi asing lebih diuntungkan daripada pengusaha lokal.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan akses permodalan untuk startup.</t>
+  </si>
+  <si>
+    <t>Sistem perpajakan yang rumit dan membingungkan masyarakat.</t>
+  </si>
+  <si>
+    <t>Tingginya biaya produksi menghambat pertumbuhan industri.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses ke teknologi modern di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya dukungan untuk pelatihan keterampilan dari pemerintah terhadap masyarakat.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses layanan keuangan seperti kredit usaha.</t>
+  </si>
+  <si>
+    <t>Krisis ekonomi membuat banyak usaha gulung tikar dan ekonomi sulit.</t>
+  </si>
+  <si>
+    <t>Kurangnya diversifikasi ekonomi mengandalkan sektor tertentu.</t>
+  </si>
+  <si>
+    <t>Harga properti yang tinggi sulit dijangkau generasi muda.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya komunikasi dan akses internet yang terbatas.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses pasar ekspor bagi para pelaku usaha kecil.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang menyebabkan kerusakan kendaraan masyarakat.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses air bersih di daerah kami menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Listrik sering mati, mengganggu aktivitas sehari-hari.</t>
+  </si>
+  <si>
+    <t>Jembatan rusak menghambat mobilitas warga desa yang berlalu lalang.</t>
+  </si>
+  <si>
+    <t>Transportasi umum tidak terjangkau dan tidak nyaman.</t>
+  </si>
+  <si>
+    <t>Drainase buruk menyebabkan banjir saat hujan deras melanda.</t>
+  </si>
+  <si>
+    <t>Fasilitas kesehatan minim, sulit mendapatkan perawatan.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses internet di daerah pedesaan membuat warga kesulitan.</t>
+  </si>
+  <si>
+    <t>Sekolah dalam kondisi rusak, kurang memadai bagi masyarakat.</t>
+  </si>
+  <si>
+    <t>Tempat sampah jarang disediakan, lingkungan kotor.</t>
+  </si>
+  <si>
+    <t>Kereta api sering terlambat, merugikan para penumpang.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat rekreasi atau taman di sekitar desa.</t>
+  </si>
+  <si>
+    <t>Kualitas udara buruk karena minimnya pohon dan vegetasi.</t>
+  </si>
+  <si>
+    <t>Jalur pejalan kaki tidak aman untuk digunakan bagi warga.</t>
+  </si>
+  <si>
+    <t>Kurangnya lampu jalan membuat malam hari gelap dan rawan.</t>
+  </si>
+  <si>
+    <t>Tidak ada sarana olahraga atau lapangan untuk warga.</t>
+  </si>
+  <si>
+    <t>Fasilitas perbelanjaan terbatas, harus pergi jauh untuk belanja.</t>
+  </si>
+  <si>
+    <t>Kerusakan infrastruktur menyulitkan petani dalam mengangkut hasil pertanian.</t>
+  </si>
+  <si>
+    <t>Keterbatasan tempat parkir di pusat desa kami sangat menyulitkan.</t>
+  </si>
+  <si>
+    <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
+  </si>
+  <si>
+    <t>Kualitas jaringan telepon seluler buruk di beberapa area.</t>
+  </si>
+  <si>
+    <t>Minimnya jalur sepeda membuat sulit bagi pengendara sepeda.</t>
+  </si>
+  <si>
+    <t>kondisi jalan yang kumuh dan tidak terawat rawan-.</t>
+  </si>
+  <si>
+    <t>Kelistrikan sering terganggu akibat cuaca ekstrem.</t>
+  </si>
+  <si>
+    <t>Pembangunan trotoar yang tidak merata dan berbahaya.</t>
+  </si>
+  <si>
+    <t>Tidak ada jalur khusus transportasi umum, menyebabkan kemacetan.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat penampungan untuk hewan jalanan di jalan.</t>
+  </si>
+  <si>
+    <t>Pipa air tua sering bocor dan mengganggu pasokan air.</t>
+  </si>
+  <si>
+    <t>Keterbatasan aksesibilitas bagi penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan pendapatan dan kesenjangan sosial yang semakin lebar, menciptakan keresahan di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap layanan kesehatan berkualitas, membuat banyak orang kesulitan mendapatkan perawatan yang dibutuhkan.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja dan peluang ekonomi yang memadai, meningkatkan tingkat pengangguran dan ketidakpastian pekerjaan.</t>
+  </si>
+  <si>
+    <t>Sistem pendidikan yang tidak merata dan kurang berkualitas, menghambat kemajuan sosial dan ekonomi bagi sebagian masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>RASWI</t>
+  </si>
+  <si>
+    <t>INOH</t>
+  </si>
+  <si>
+    <t>MUSLIHIN</t>
+  </si>
+  <si>
+    <t>USMAN</t>
+  </si>
+  <si>
+    <t>HANIAH</t>
+  </si>
+  <si>
+    <t>MUMU ABDUL MUIN</t>
+  </si>
+  <si>
+    <t>LIA WATI</t>
+  </si>
+  <si>
+    <t>MILA MUAWALIAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD LUTFI AZIZ</t>
+  </si>
+  <si>
+    <t>WAHAB HABIBULLOH</t>
+  </si>
+  <si>
+    <t>YOYOH NURSOLIHAH</t>
+  </si>
+  <si>
+    <t>ZIDNY FATHURROHMAN</t>
+  </si>
+  <si>
+    <t>ALYA ASMA NABILA</t>
+  </si>
+  <si>
+    <t>UMAR</t>
+  </si>
+  <si>
+    <t>SUKAESIH</t>
+  </si>
+  <si>
+    <t>YAYA AULIA</t>
+  </si>
+  <si>
+    <t>DIDI JUNAEDI</t>
+  </si>
+  <si>
+    <t>JENAL</t>
+  </si>
+  <si>
+    <t>NIA KURNIATI</t>
+  </si>
+  <si>
+    <t>RISNA</t>
+  </si>
+  <si>
+    <t>RISNO</t>
+  </si>
+  <si>
+    <t>AHYAR</t>
+  </si>
+  <si>
+    <t>ROHMAN</t>
+  </si>
+  <si>
+    <t>OJOH</t>
+  </si>
+  <si>
+    <t>IPAN NOOR AJIZ</t>
+  </si>
+  <si>
+    <t>ENDAH NURAJIJAH</t>
+  </si>
+  <si>
+    <t>ROMLI</t>
+  </si>
+  <si>
+    <t>OYOH</t>
+  </si>
+  <si>
+    <t>TATI</t>
+  </si>
+  <si>
+    <t>NANA SUTISNA</t>
+  </si>
+  <si>
+    <t>JUANDA HERDIANSYAH SAPUTRA</t>
+  </si>
+  <si>
+    <t>RAHMAT</t>
+  </si>
+  <si>
+    <t>LILIS SURYANI</t>
+  </si>
+  <si>
+    <t>RAIGINA SYAKILA MUSTIKA</t>
+  </si>
+  <si>
+    <t>ANANG</t>
+  </si>
+  <si>
+    <t>SITI SOPIAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD RIFQI</t>
+  </si>
+  <si>
+    <t>KURDI</t>
+  </si>
+  <si>
+    <t>SITI ASIYAH</t>
+  </si>
+  <si>
+    <t>RINI APRIYANI</t>
+  </si>
+  <si>
+    <t>TAOPIK HIDAYATULLOH</t>
+  </si>
+  <si>
+    <t>MUHAMAD ALIF FIKRI</t>
+  </si>
+  <si>
+    <t>YOYO</t>
+  </si>
+  <si>
+    <t>ENUR</t>
+  </si>
+  <si>
+    <t>MAMAY</t>
+  </si>
+  <si>
+    <t>TARMAN</t>
+  </si>
+  <si>
+    <t>DAYITI</t>
+  </si>
+  <si>
+    <t>SURWITI</t>
+  </si>
+  <si>
+    <t>MARYAH</t>
+  </si>
+  <si>
+    <t>WARSO WIHARMA PUTRA</t>
+  </si>
+  <si>
+    <t>ICIH BIN SUHARYA</t>
+  </si>
+  <si>
+    <t>UHA</t>
+  </si>
+  <si>
+    <t>DEDEH KURNIASIH</t>
+  </si>
+  <si>
+    <t>NURLAELASARI</t>
+  </si>
+  <si>
+    <t>AMELIA TRESNA LESTARI</t>
+  </si>
+  <si>
+    <t>AGUS</t>
+  </si>
+  <si>
+    <t>EMAY MARYATI</t>
+  </si>
+  <si>
+    <t>MIA NURUL KHORIYAH</t>
+  </si>
+  <si>
+    <t>IPAN NURDIN</t>
+  </si>
+  <si>
+    <t>RASJA SUPRIATNA</t>
+  </si>
+  <si>
+    <t>MUMUN MUNAWAROH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FARHANULIBAD</t>
+  </si>
+  <si>
+    <t>AZKIA TRI AMALIA</t>
+  </si>
+  <si>
+    <t>AHIDIN</t>
+  </si>
+  <si>
+    <t>ETI</t>
+  </si>
+  <si>
+    <t>ADE RIZAL</t>
+  </si>
+  <si>
+    <t>TATA</t>
+  </si>
+  <si>
+    <t>CARSIH</t>
+  </si>
+  <si>
+    <t>2023-08-15</t>
+  </si>
+  <si>
+    <t>2023-08-16</t>
+  </si>
+  <si>
+    <t>2023-08-17</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>2023-08-19</t>
+  </si>
+  <si>
+    <t>2023-08-21</t>
+  </si>
+  <si>
+    <t>2023-08-22</t>
+  </si>
+  <si>
+    <t>2023-08-23</t>
   </si>
 </sst>
 </file>
@@ -1041,29 +999,29 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Cacaban</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>008</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I2">
         <f>LEN(H2)</f>
@@ -1075,33 +1033,33 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Cacaban</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>003</v>
       </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I31" si="0">LEN(H3)</f>
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -1109,33 +1067,33 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>005</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>009</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -1143,33 +1101,33 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Garunggang</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>009</v>
       </c>
-      <c r="F5" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
-      </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1177,10 +1135,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -1188,22 +1146,22 @@
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>007</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>002</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -1211,33 +1169,33 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sindang</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>013</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -1245,18 +1203,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Garunggang</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>010</v>
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1267,11 +1225,11 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1279,33 +1237,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>011</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1313,33 +1271,33 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cipinang</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>011</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>006</v>
       </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1347,33 +1305,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Sindang</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>003</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1381,10 +1339,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -1392,22 +1350,22 @@
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>014</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>003</v>
       </c>
       <c r="G12" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1415,14 +1373,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Garunggang</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1430,18 +1388,18 @@
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1449,33 +1407,33 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Garunggang</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>009</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>008</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1483,33 +1441,33 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>004</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>006</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I15">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1517,33 +1475,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Cipinang</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>007</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>010</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I16">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1551,33 +1509,33 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Sindang</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="F17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>007</v>
       </c>
       <c r="G17" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I17">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1585,33 +1543,33 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Mandala</v>
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>007</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>005</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I18">
         <f t="shared" si="0"/>
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1619,18 +1577,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>015</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1641,11 +1599,11 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I19">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1653,33 +1611,33 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>008</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I20">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1687,33 +1645,33 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Mandala</v>
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>004</v>
       </c>
-      <c r="F21" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
-      </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I21">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1721,33 +1679,33 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>007</v>
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>006</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I22">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1755,33 +1713,33 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>014</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>003</v>
       </c>
       <c r="G23" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I23">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1789,33 +1747,33 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Sindang</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>010</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>008</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I24">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1823,18 +1781,18 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="F25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1845,11 +1803,11 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I25">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1857,33 +1815,33 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="D26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Mandala</v>
       </c>
       <c r="E26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>013</v>
       </c>
       <c r="F26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>005</v>
       </c>
       <c r="G26" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I26">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1891,33 +1849,33 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="D27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Mandala</v>
       </c>
       <c r="E27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>010</v>
       </c>
       <c r="F27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>004</v>
       </c>
       <c r="G27" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H27" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I27">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1925,10 +1883,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="D28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -1936,22 +1894,22 @@
       </c>
       <c r="E28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>014</v>
       </c>
       <c r="F28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>013</v>
       </c>
       <c r="G28" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I28">
         <f t="shared" si="0"/>
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1959,22 +1917,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="D29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cipinang</v>
       </c>
       <c r="E29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>004</v>
       </c>
       <c r="F29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G29" s="4" t="str">
         <f>conf!$A$2</f>
@@ -1985,7 +1943,7 @@
       </c>
       <c r="I29">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1993,33 +1951,33 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="D30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Garunggang</v>
       </c>
       <c r="E30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>011</v>
       </c>
       <c r="F30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>007</v>
       </c>
       <c r="G30" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="I30">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -2027,18 +1985,18 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Sindang</v>
       </c>
       <c r="E31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>007</v>
       </c>
       <c r="F31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2049,127 +2007,127 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H31" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I31">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="D32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Garunggang</v>
       </c>
       <c r="E32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>003</v>
       </c>
       <c r="F32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>003</v>
       </c>
       <c r="G32" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="D33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Cacaban</v>
       </c>
       <c r="E33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>011</v>
       </c>
       <c r="F33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>012</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H33" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="D34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Mandala</v>
       </c>
       <c r="E34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="F34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>002</v>
       </c>
       <c r="G34" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>138</v>
+      <c r="H34" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>013</v>
       </c>
       <c r="F35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>139</v>
+      <c r="H35" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -2177,169 +2135,169 @@
       </c>
       <c r="E36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="F36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="G36" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>140</v>
+      <c r="H36" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="D37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>007</v>
       </c>
       <c r="F37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>002</v>
       </c>
       <c r="G37" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>141</v>
+      <c r="H37" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="D38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Cipinang</v>
       </c>
       <c r="E38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>003</v>
       </c>
-      <c r="F38" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
-      </c>
       <c r="G38" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>142</v>
+      <c r="H38" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="D39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Mandala</v>
       </c>
       <c r="E39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>006</v>
       </c>
       <c r="G39" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>143</v>
+      <c r="H39" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Cacaban</v>
       </c>
       <c r="E40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>014</v>
       </c>
-      <c r="F40" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
-      </c>
       <c r="G40" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>144</v>
+      <c r="H40" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>001</v>
       </c>
-      <c r="F41" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
-      </c>
       <c r="G41" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>145</v>
+      <c r="H41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>013</v>
       </c>
       <c r="F42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2350,258 +2308,258 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H42" t="s">
-        <v>146</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Garunggang</v>
       </c>
       <c r="E43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="F43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="G43" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>147</v>
+      <c r="H43" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="D44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>005</v>
       </c>
       <c r="F44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>006</v>
       </c>
       <c r="G44" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>148</v>
+      <c r="H44" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="D45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Mandala</v>
       </c>
       <c r="E45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>013</v>
       </c>
       <c r="F45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>013</v>
       </c>
       <c r="G45" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>149</v>
+      <c r="H45" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Cacaban</v>
       </c>
       <c r="E46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="F46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>012</v>
       </c>
       <c r="G46" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>150</v>
+      <c r="H46" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Sindang</v>
       </c>
       <c r="E47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>009</v>
       </c>
       <c r="F47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>005</v>
       </c>
       <c r="G47" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>151</v>
+      <c r="H47" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="D48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Sindang</v>
       </c>
       <c r="E48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>001</v>
       </c>
       <c r="F48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>012</v>
       </c>
       <c r="G48" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>152</v>
+      <c r="H48" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="D49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Garunggang</v>
       </c>
       <c r="E49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>003</v>
       </c>
       <c r="F49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="G49" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>153</v>
+      <c r="H49" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Mandala</v>
       </c>
       <c r="E50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>001</v>
       </c>
       <c r="F50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G50" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>154</v>
+      <c r="H50" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Sindang</v>
       </c>
       <c r="E51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>003</v>
       </c>
       <c r="F51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="G51" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H51" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -2609,165 +2567,165 @@
       </c>
       <c r="E52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="F52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>004</v>
       </c>
       <c r="G52" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>156</v>
+      <c r="H52" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="D53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>007</v>
       </c>
       <c r="F53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G53" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H53" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Cacaban</v>
       </c>
       <c r="E54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>007</v>
       </c>
       <c r="F54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>008</v>
       </c>
       <c r="G54" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>001</v>
       </c>
       <c r="F55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>003</v>
       </c>
       <c r="G55" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H55" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="D56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Sindangjaya</v>
       </c>
       <c r="E56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>003</v>
       </c>
       <c r="F56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>009</v>
       </c>
       <c r="G56" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H56" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="D57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Cipinang</v>
       </c>
       <c r="E57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="F57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="G57" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H57" t="s">
-        <v>161</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="D58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -2775,49 +2733,49 @@
       </c>
       <c r="F58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="G58" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H58" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="D59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Garunggang</v>
       </c>
       <c r="E59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>009</v>
       </c>
       <c r="G59" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H59" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="D60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -2829,84 +2787,84 @@
       </c>
       <c r="F60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>009</v>
       </c>
       <c r="G60" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H60" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="D61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>003</v>
       </c>
       <c r="G61" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H61" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="D62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="F62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>009</v>
       </c>
       <c r="G62" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H62" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="D63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Cacaban</v>
       </c>
       <c r="E63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>007</v>
       </c>
       <c r="F63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2917,123 +2875,123 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H63" t="s">
-        <v>167</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>004</v>
       </c>
       <c r="F64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>002</v>
       </c>
       <c r="G64" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H64" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="D65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Cacaban</v>
       </c>
       <c r="E65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>012</v>
       </c>
       <c r="F65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>010</v>
       </c>
       <c r="G65" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H65" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="D66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>012</v>
       </c>
       <c r="F66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>002</v>
       </c>
       <c r="G66" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H66" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="D67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
+        <v>Sukamaju</v>
       </c>
       <c r="E67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>008</v>
       </c>
       <c r="F67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>010</v>
       </c>
       <c r="G67" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H67" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -3041,61 +2999,61 @@
       </c>
       <c r="E68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>001</v>
       </c>
       <c r="F68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>011</v>
       </c>
       <c r="G68" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H68" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="D69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>015</v>
       </c>
       <c r="F69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>007</v>
       </c>
       <c r="G69" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H69" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="D70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sindang</v>
       </c>
       <c r="E70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>014</v>
       </c>
       <c r="F70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -3106,15 +3064,15 @@
         <v>Tanjungsari</v>
       </c>
       <c r="H70" t="s">
-        <v>174</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -3122,154 +3080,54 @@
       </c>
       <c r="E71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="F71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="G71" s="4" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H71" t="s">
-        <v>175</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B72" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindang</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
-      </c>
-      <c r="F72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
-      </c>
-      <c r="G72" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H72" t="s">
-        <v>176</v>
-      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="4"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B73" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
-      </c>
-      <c r="F73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
-      </c>
-      <c r="G73" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H73" t="s">
-        <v>177</v>
-      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="4"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
-      </c>
-      <c r="F74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
-      </c>
-      <c r="G74" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H74" t="s">
-        <v>178</v>
-      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B75" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
-      </c>
-      <c r="F75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
-      </c>
-      <c r="G75" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H75" t="s">
-        <v>179</v>
-      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B76" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
-      </c>
-      <c r="F76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
-      </c>
-      <c r="G76" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H76" t="s">
-        <v>180</v>
-      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test/list/rajadesa/tanjungsari/list_tanjungsari_2.xlsx
+++ b/test/list/rajadesa/tanjungsari/list_tanjungsari_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\rajadesa\tanjungsari\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D527AE6-C3F1-45D9-AB47-B0AE26DAB3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CF33AE-78E3-4C7C-9E7E-E522EFDA5D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="conf" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="149">
   <si>
     <t>nama</t>
   </si>
@@ -172,64 +183,307 @@
     <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
   </si>
   <si>
-    <t>RAHMAT</t>
-  </si>
-  <si>
-    <t>SRI MASNUAH</t>
-  </si>
-  <si>
-    <t>YOHAN SUWANDANA</t>
-  </si>
-  <si>
-    <t>EVA NURMALASARI</t>
-  </si>
-  <si>
-    <t>ARDAN SOFYAN MALIK</t>
-  </si>
-  <si>
-    <t>JUJU JUANDA</t>
-  </si>
-  <si>
-    <t>ININ SANIAH</t>
-  </si>
-  <si>
-    <t>FELYCIA AZKADINA NAZIFA</t>
-  </si>
-  <si>
-    <t>KAYLA AZKA SHIFARA</t>
-  </si>
-  <si>
-    <t>HAMID</t>
-  </si>
-  <si>
-    <t>LILIH</t>
-  </si>
-  <si>
-    <t>ALI</t>
-  </si>
-  <si>
-    <t>SINTA</t>
-  </si>
-  <si>
-    <t>YAJID</t>
-  </si>
-  <si>
-    <t>ROJULI TOLIBI</t>
-  </si>
-  <si>
-    <t>HENI</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>2023-09-06</t>
-  </si>
-  <si>
-    <t>2023-09-07</t>
-  </si>
-  <si>
-    <t>2023-09-08</t>
+    <t>Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>menurut $nama Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>Harga kebutuhan pokok naik terus, sulit untuk mencukupi kebutuhan sehari-hari.</t>
+  </si>
+  <si>
+    <t>Pekerjaan sulit dicari, pengangguran meningkat di wilayah ini.</t>
+  </si>
+  <si>
+    <t>Biaya pendidikan mahal, sulit bagi keluarga kurang mampu.</t>
+  </si>
+  <si>
+    <t>Persaingan usaha tidak sehat, usaha kecil sulit bertahan.</t>
+  </si>
+  <si>
+    <t>Banyak produk palsu, merugikan konsumen dan produsen asli.</t>
+  </si>
+  <si>
+    <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
+  </si>
+  <si>
+    <t>Birokrasi perizinan usaha sulit dan memakan waktu.</t>
+  </si>
+  <si>
+    <t>Ketimpangan sosial dan ekonomi semakin besar, kesenjangan kaya-miskin.</t>
+  </si>
+  <si>
+    <t>Jalan rusak parah, mengganggu kelancaran lalu lintas dan merusak kendaraan.</t>
+  </si>
+  <si>
+    <t>Kemacetan lalu lintas yang parah, menyebabkan waktu tempuh yang lama.</t>
+  </si>
+  <si>
+    <t>Kurangnya perawatan rutin, membuat jalan semakin buruk.</t>
+  </si>
+  <si>
+    <t>Kurangnya penyeberangan pejalan kaki dan fasilitas untuk penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Kebutuhan perluasan jalan tidak terpenuhi, menyebabkan kemacetan terus bertambah.</t>
+  </si>
+  <si>
+    <t>Kurangnya penerangan jalan yang memadai, meningkatkan risiko kecelakaan di malam hari.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang yang berbahaya bagi pengendara sepeda motor dan pengguna jalan lainnya.</t>
+  </si>
+  <si>
+    <t>Kurangnya trotoar yang aman, mengancam keselamatan pejalan kaki.</t>
+  </si>
+  <si>
+    <t>Parkir liar yang menghalangi akses jalan dan mengurangi ruang untuk kendaraan.</t>
+  </si>
+  <si>
+    <t>Kurangnya rambu lalu lintas yang jelas dan terawat, membingungkan pengguna jalan.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jalur sepeda yang aman, menghambat pengembangan transportasi berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Kendaraan parkir sembarangan di jalan, menyebabkan kemacetan dan kekacauan.</t>
+  </si>
+  <si>
+    <t>Jalan tidak terlayani saat hujan, menyebabkan banjir dan genangan air.</t>
+  </si>
+  <si>
+    <t>Tidak adanya fasilitas penyeberangan untuk hewan di jalan raya.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>2023-10-10</t>
+  </si>
+  <si>
+    <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>2023-10-12</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-10-14</t>
+  </si>
+  <si>
+    <t>2023-10-16</t>
+  </si>
+  <si>
+    <t>2023-10-17</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>2023-10-19</t>
+  </si>
+  <si>
+    <t>2023-10-20</t>
+  </si>
+  <si>
+    <t>2023-10-21</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>2023-10-24</t>
+  </si>
+  <si>
+    <t>NENGSIH WARNENGSIH</t>
+  </si>
+  <si>
+    <t>FAJRI GUNAWAN</t>
+  </si>
+  <si>
+    <t>MARTIN BUDIMAN</t>
+  </si>
+  <si>
+    <t>NYAI PATIMAH</t>
+  </si>
+  <si>
+    <t>LUCKY BUDIMAN</t>
+  </si>
+  <si>
+    <t>DIDI</t>
+  </si>
+  <si>
+    <t>YAYAH</t>
+  </si>
+  <si>
+    <t>ENDAH LATIFATUL JANAH</t>
+  </si>
+  <si>
+    <t>IIP PAUZI LATIF</t>
+  </si>
+  <si>
+    <t>WAHYU HIDAYAT</t>
+  </si>
+  <si>
+    <t>CICIH WIARSIH</t>
+  </si>
+  <si>
+    <t>NENI SRI SUMARNI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD SYAFIQ RAMADANI</t>
+  </si>
+  <si>
+    <t>ZIDAN RIZKI RAMADHAN</t>
+  </si>
+  <si>
+    <t>IDA MARDIATUL LAILA</t>
+  </si>
+  <si>
+    <t>FAEYZA ARSYAD ZHAFIR</t>
+  </si>
+  <si>
+    <t>SIDIK</t>
+  </si>
+  <si>
+    <t>NURHAYATI</t>
+  </si>
+  <si>
+    <t>ALDI</t>
+  </si>
+  <si>
+    <t>TEGUH FIRMANSYAH</t>
+  </si>
+  <si>
+    <t>ARI SETIAWAN</t>
+  </si>
+  <si>
+    <t>KARTIKA RAHAYU ALAM</t>
+  </si>
+  <si>
+    <t>AKBAR MUHAMMAD RAMADHAN</t>
+  </si>
+  <si>
+    <t>EROH JUHAERAH</t>
+  </si>
+  <si>
+    <t>Hj. SAIROH</t>
+  </si>
+  <si>
+    <t>ROPIAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD RIZKI</t>
+  </si>
+  <si>
+    <t>EKA PURNAWAN</t>
+  </si>
+  <si>
+    <t>AZHA FAUZIAH</t>
+  </si>
+  <si>
+    <t>RAVISA ATQIANI PURNAWAN</t>
+  </si>
+  <si>
+    <t>ENDI JUNAEDI</t>
+  </si>
+  <si>
+    <t>MAYASARI</t>
+  </si>
+  <si>
+    <t>ERISKA KANIZA ALVIANINDI</t>
+  </si>
+  <si>
+    <t>AGUS DARMAWAN</t>
+  </si>
+  <si>
+    <t>NURUL AULIA</t>
+  </si>
+  <si>
+    <t>DZAKIRA ANDITA DARMAWAN</t>
+  </si>
+  <si>
+    <t>SOMA ATMAJA</t>
+  </si>
+  <si>
+    <t>ELIS LISNAWATI</t>
+  </si>
+  <si>
+    <t>ELSA USWATUN NAZWA</t>
+  </si>
+  <si>
+    <t>NURDIN</t>
+  </si>
+  <si>
+    <t>EPIN MUPIDAH</t>
+  </si>
+  <si>
+    <t>SALMAN</t>
+  </si>
+  <si>
+    <t>SARTINI</t>
+  </si>
+  <si>
+    <t>DEA APRILIANI</t>
+  </si>
+  <si>
+    <t>SAEPUL ANWAR</t>
+  </si>
+  <si>
+    <t>YAYU KODSIYAH</t>
+  </si>
+  <si>
+    <t>RIVAN NUR MULQI</t>
+  </si>
+  <si>
+    <t>DARMAD</t>
+  </si>
+  <si>
+    <t>SUMIATI</t>
+  </si>
+  <si>
+    <t>ALYA AINUN NAZLAH</t>
+  </si>
+  <si>
+    <t>SAWARDI</t>
+  </si>
+  <si>
+    <t>ADE SRIMULYA</t>
+  </si>
+  <si>
+    <t>SAEP</t>
+  </si>
+  <si>
+    <t>ERNI ERNAWATI</t>
+  </si>
+  <si>
+    <t>ELSA JULIYANTI</t>
+  </si>
+  <si>
+    <t>SILVIA AGESTI</t>
   </si>
 </sst>
 </file>
@@ -237,7 +491,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -286,16 +540,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Mata Uang" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -323,7 +580,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -619,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -660,33 +917,33 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Kubangsari</v>
+        <v>Sindang</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>010</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I2">
         <f>LEN(H2)</f>
-        <v>56</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -694,33 +951,33 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Sindang</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>012</v>
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>001</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I17" si="0">LEN(H3)</f>
-        <v>57</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -728,33 +985,33 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sindang</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>005</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>007</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H4" t="s">
-        <v>34</v>
+      <c r="H4" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -762,33 +1019,33 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Sindang</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>003</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>015</v>
       </c>
       <c r="G5" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H5" t="s">
-        <v>35</v>
+      <c r="H5" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -796,10 +1053,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
@@ -807,22 +1064,22 @@
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>015</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>010</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
+      <c r="H6" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -830,33 +1087,33 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Mandala</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>015</v>
       </c>
-      <c r="F7" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
-      </c>
       <c r="G7" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H7" t="s">
-        <v>37</v>
+      <c r="H7" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -864,14 +1121,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Sindang</v>
       </c>
       <c r="E8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -885,12 +1142,12 @@
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H8" t="s">
-        <v>38</v>
+      <c r="H8" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -898,33 +1155,33 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Cipinang</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>002</v>
       </c>
       <c r="G9" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H9" t="s">
-        <v>39</v>
+      <c r="H9" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -932,33 +1189,33 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Garunggang</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>001</v>
       </c>
       <c r="F10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>010</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H10" t="s">
-        <v>40</v>
+      <c r="H10" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -966,33 +1223,33 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cacaban</v>
+        <v>Mandala</v>
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>005</v>
       </c>
       <c r="G11" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H11" t="s">
-        <v>41</v>
+      <c r="H11" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1000,33 +1257,33 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>008</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="G12" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1034,33 +1291,33 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Garunggang</v>
+        <v>Cacaban</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>002</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="G13" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H13" t="s">
-        <v>43</v>
+      <c r="H13" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1068,33 +1325,33 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sindangjaya</v>
+        <v>Kubangsari</v>
       </c>
       <c r="E14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
+        <v>004</v>
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="G14" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H14" t="s">
-        <v>44</v>
+      <c r="H14" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1102,33 +1359,33 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Sukamaju</v>
+        <v>Garunggang</v>
       </c>
       <c r="E15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>001</v>
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>014</v>
       </c>
       <c r="G15" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H15" t="s">
-        <v>45</v>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="I15">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1136,33 +1393,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Mandala</v>
+        <v>Cipinang</v>
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
+        <v>004</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>007</v>
       </c>
       <c r="G16" s="3" t="str">
         <f>conf!$A$2</f>
         <v>Tanjungsari</v>
       </c>
-      <c r="H16" t="s">
-        <v>46</v>
+      <c r="H16" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="I16">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1170,33 +1427,1113 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
-        <v>Cipinang</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
-      </c>
-      <c r="F17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
-      <c r="G17" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v>Tanjungsari</v>
-      </c>
-      <c r="H17" t="s">
-        <v>47</v>
       </c>
       <c r="I17">
         <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cacaban</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cacaban</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cacaban</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>123</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cacaban</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H33" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Garunggang</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H35" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindang</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Garunggang</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sukamaju</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H40" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sukamaju</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Kubangsari</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Garunggang</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindangjaya</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Mandala</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindang</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cipinang</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Cacaban</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H52" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Garunggang</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>013</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H53" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sukamaju</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindang</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sindang</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H56" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,8),1)</f>
+        <v>Sukamaju</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G57" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v>Tanjungsari</v>
+      </c>
+      <c r="H57" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
